--- a/outputs/programacion_matriz.xlsx
+++ b/outputs/programacion_matriz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\git\Trabajos\programacion_academica\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BF06B4-E5D6-406F-9D6D-9FF5C105A79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A220B64-08D3-4339-9EBE-2FDE4284AF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1817,13 +1817,15 @@
       <c r="BB8" s="13">
         <v>2</v>
       </c>
-      <c r="BC8" s="13"/>
+      <c r="BC8" s="13">
+        <v>3</v>
+      </c>
       <c r="BD8" s="12"/>
       <c r="BE8" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BF8" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BG8" s="16">
         <f t="shared" si="0"/>
@@ -1836,7 +1838,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BJ8" s="18" t="str">
+      <c r="BJ8" s="17" t="str">
         <f t="shared" si="2"/>
         <v>Completa</v>
       </c>
@@ -1928,7 +1930,7 @@
       <c r="AX9" s="12"/>
       <c r="AY9" s="12"/>
       <c r="AZ9" s="12">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BA9" s="13"/>
       <c r="BB9" s="13"/>
@@ -1937,7 +1939,9 @@
       </c>
       <c r="BD9" s="12"/>
       <c r="BE9" s="12"/>
-      <c r="BF9" s="12"/>
+      <c r="BF9" s="12">
+        <v>3</v>
+      </c>
       <c r="BG9" s="16">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -2038,7 +2042,9 @@
       <c r="AY10" s="12">
         <v>2</v>
       </c>
-      <c r="AZ10" s="12"/>
+      <c r="AZ10" s="12">
+        <v>3</v>
+      </c>
       <c r="BA10" s="13"/>
       <c r="BB10" s="13">
         <v>2</v>
@@ -2050,9 +2056,7 @@
       <c r="BE10" s="12">
         <v>3</v>
       </c>
-      <c r="BF10" s="12">
-        <v>3</v>
-      </c>
+      <c r="BF10" s="12"/>
       <c r="BG10" s="16">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -2680,19 +2684,19 @@
       </c>
       <c r="BC16" s="19">
         <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="BD16" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="BE16" s="19">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="BF16" s="19">
+        <f t="shared" si="4"/>
         <v>6</v>
-      </c>
-      <c r="BD16" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BE16" s="19">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="BF16" s="19">
-        <f t="shared" si="4"/>
-        <v>7</v>
       </c>
     </row>
   </sheetData>
